--- a/tests/amostras/xp_fatura.xlsx
+++ b/tests/amostras/xp_fatura.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OTICA NOVALENTES LTDA</t>
+          <t>OTICA CENTRAL LTDA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ROSANGELA TITULAR</t>
+          <t>RO TITULAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ROSANGELA TITULAR</t>
+          <t>RO TITULAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WOW*WOWTJD CABELEIREIR</t>
+          <t>SALAO DE BELEZA WW</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ROSANGELA TITULAR</t>
+          <t>RO TITULAR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EINSTEIN MORUMBI</t>
+          <t>LABORATORIO CENTRAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ROSANGELA TITULAR</t>
+          <t>RO TITULAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -714,15 +714,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>6542.05</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
